--- a/data_processed/results_XGB_kg_CO2e_per_capitatenure.xlsx
+++ b/data_processed/results_XGB_kg_CO2e_per_capitatenure.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8224" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8251" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>527.4948120117188</v>
+        <v>424.7623901367188</v>
       </c>
       <c r="D2" t="n">
-        <v>20.47612762451172</v>
+        <v>14.54803657531738</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>274.0771484375</v>
+        <v>497.4569396972656</v>
       </c>
       <c r="D3" t="n">
-        <v>10.63904094696045</v>
+        <v>17.03781318664551</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>140.1710052490234</v>
+        <v>521.189697265625</v>
       </c>
       <c r="D4" t="n">
-        <v>5.44111442565918</v>
+        <v>17.85065460205078</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>246.4806060791016</v>
+        <v>380.8933715820312</v>
       </c>
       <c r="D5" t="n">
-        <v>9.567807197570801</v>
+        <v>13.04553031921387</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>163.0265350341797</v>
+        <v>47.75934982299805</v>
       </c>
       <c r="D6" t="n">
-        <v>6.328312873840332</v>
+        <v>1.635749340057373</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>59.61563110351562</v>
+        <v>164.6771697998047</v>
       </c>
       <c r="D7" t="n">
-        <v>2.314140796661377</v>
+        <v>5.640163898468018</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_train</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>805.49609375</v>
+        <v>177.7678527832031</v>
       </c>
       <c r="D8" t="n">
-        <v>31.26749420166016</v>
+        <v>6.088517189025879</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>291.6344299316406</v>
+        <v>128.6019134521484</v>
       </c>
       <c r="D9" t="n">
-        <v>11.3205738067627</v>
+        <v>4.404592990875244</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>districtheating_pc</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.14894104003906</v>
+        <v>126.0773849487305</v>
       </c>
       <c r="D10" t="n">
-        <v>2.645384311676025</v>
+        <v>4.318128108978271</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heatpump_pc</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>54.70348358154297</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.873584508895874</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>solarcapacity</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>395.8339233398438</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13.55724143981934</v>
       </c>
     </row>
   </sheetData>
